--- a/artfynd/A 1237-2026 artfynd.xlsx
+++ b/artfynd/A 1237-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323034</v>
+        <v>120323032</v>
       </c>
       <c r="B2" t="n">
-        <v>97931</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494385</v>
+        <v>494376</v>
       </c>
       <c r="R2" t="n">
-        <v>6672376</v>
+        <v>6672381</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120323032</v>
+        <v>120323033</v>
       </c>
       <c r="B3" t="n">
-        <v>97931</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494376</v>
+        <v>494390</v>
       </c>
       <c r="R3" t="n">
-        <v>6672381</v>
+        <v>6672363</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,6 +874,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120323034</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Låsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>494385</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6672376</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Oskar Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Oskar Persson, Elliot Örjes, Frida Sjöborg, Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
